--- a/Data/INSAR_data.xlsx
+++ b/Data/INSAR_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10720"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://csiroau-my.sharepoint.com/personal/lin253_csiro_au/Documents/China Coastline/Manuscript/China_database_YC_LIN/Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://csiroau-my.sharepoint.com/personal/lin253_csiro_au/Documents/China Coastline/Manuscript/Submission 3/China_database_YC_LIN_v3/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{21F84809-CF14-894D-A2FF-DE73736BF5ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DB7F827-FDE3-7E4D-BB02-1A516EDA8BE0}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{21F84809-CF14-894D-A2FF-DE73736BF5ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FBCD700C-92BC-F24D-962E-C5EF02D8A6DE}"/>
   <bookViews>
-    <workbookView xWindow="30240" yWindow="3720" windowWidth="51200" windowHeight="28300" activeTab="1" xr2:uid="{2ADC1102-C41A-5D40-B105-A55803D19B76}"/>
+    <workbookView xWindow="30240" yWindow="500" windowWidth="51200" windowHeight="28300" activeTab="1" xr2:uid="{2ADC1102-C41A-5D40-B105-A55803D19B76}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -310,9 +310,6 @@
   </si>
   <si>
     <t>95th</t>
-  </si>
-  <si>
-    <t>Lin et al. (2025), "Profound modern sea-level evolution against geological backdrop in southeastern China"</t>
   </si>
   <si>
     <t>Modern InSAR VLM database for</t>
@@ -362,6 +359,9 @@
   </si>
   <si>
     <t>The database comprise InSAR measured China vertical land motion data from the following paper:</t>
+  </si>
+  <si>
+    <t>Lin et al. (2025), "Modern sea-level rise breaks 4000-year stability in southeastern China"</t>
   </si>
 </sst>
 </file>
@@ -3202,22 +3202,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" ht="176">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
       <c r="A2" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="20">
       <c r="A6" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="35">
       <c r="A8" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/Data/INSAR_data.xlsx
+++ b/Data/INSAR_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10720"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://csiroau-my.sharepoint.com/personal/lin253_csiro_au/Documents/China Coastline/Manuscript/Submission 3/China_database_YC_LIN_v3/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{21F84809-CF14-894D-A2FF-DE73736BF5ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FBCD700C-92BC-F24D-962E-C5EF02D8A6DE}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{21F84809-CF14-894D-A2FF-DE73736BF5ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F624DA44-B2DB-AF4B-AB0E-A43E367510B2}"/>
   <bookViews>
-    <workbookView xWindow="30240" yWindow="500" windowWidth="51200" windowHeight="28300" activeTab="1" xr2:uid="{2ADC1102-C41A-5D40-B105-A55803D19B76}"/>
+    <workbookView xWindow="30240" yWindow="500" windowWidth="51200" windowHeight="28300" xr2:uid="{2ADC1102-C41A-5D40-B105-A55803D19B76}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -458,6 +458,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3189,6 +3193,10 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;12&amp;KFF0000 OFFICIAL&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;12&amp;KFF0000 OFFICIAL</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -3222,5 +3230,9 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;12&amp;KFF0000 OFFICIAL&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;12&amp;KFF0000 OFFICIAL</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>